--- a/data/trans_orig/IP3106-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3106-Estudios-trans_orig.xlsx
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14083</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15644</t>
+          <t>15925</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>12652</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>12083</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25868</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -1298,49 +1298,49 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64088</t>
+          <t>63438</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>74819</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>81,56%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>74,15%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>87,45%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>70838</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>65227</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>75135</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>81,56%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>74,91%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>87,82%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>70838</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>64915</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>75044</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>86,21%</t>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>131464</t>
+          <t>132523</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>147819</t>
+          <t>147551</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10553</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23650</t>
+          <t>22530</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17728</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34834</t>
+          <t>33061</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31371</t>
+          <t>31991</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51592</t>
+          <t>53085</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66273</t>
+          <t>66208</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>91320</t>
+          <t>90776</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74905</t>
+          <t>74123</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>99550</t>
+          <t>100883</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>144988</t>
+          <t>147750</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>181948</t>
+          <t>182949</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>280053</t>
+          <t>280045</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>307614</t>
+          <t>307656</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>320401</t>
+          <t>319463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>349736</t>
+          <t>348537</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>609359</t>
+          <t>609481</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>648753</t>
+          <t>648346</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18654</t>
+          <t>18542</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11871</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>24816</t>
+          <t>25860</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>17102</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30455</t>
+          <t>32224</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>19848</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35380</t>
+          <t>35348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39579</t>
+          <t>40309</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61187</t>
+          <t>61898</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115723</t>
+          <t>116002</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>132204</t>
+          <t>133696</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>100954</t>
+          <t>100985</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>117622</t>
+          <t>117362</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>221975</t>
+          <t>222625</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>245393</t>
+          <t>245092</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,92%</t>
         </is>
       </c>
     </row>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24700</t>
+          <t>24719</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42623</t>
+          <t>43801</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>25438</t>
+          <t>25618</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44287</t>
+          <t>44580</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>54913</t>
+          <t>53570</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>81677</t>
+          <t>79851</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>96917</t>
+          <t>97225</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>127736</t>
+          <t>126981</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>105630</t>
+          <t>106891</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>137768</t>
+          <t>138194</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>212800</t>
+          <t>213394</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>257585</t>
+          <t>260536</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>471486</t>
+          <t>471538</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>504997</t>
+          <t>503844</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>498062</t>
+          <t>498008</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>532229</t>
+          <t>533389</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>976950</t>
+          <t>977441</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1027620</t>
+          <t>1026409</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>792</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>11946</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>17394</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69707</t>
+          <t>70075</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80779</t>
+          <t>80907</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68516</t>
+          <t>68438</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>78514</t>
+          <t>78348</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>142133</t>
+          <t>141551</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>156580</t>
+          <t>156948</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17831</t>
+          <t>17225</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20409</t>
+          <t>19476</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16018</t>
+          <t>16085</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33303</t>
+          <t>32868</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14637</t>
+          <t>14238</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>28344</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22623</t>
+          <t>22510</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40714</t>
+          <t>41171</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>41769</t>
+          <t>41640</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>66317</t>
+          <t>64460</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>370382</t>
+          <t>370953</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>389159</t>
+          <t>388948</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>396206</t>
+          <t>395717</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>417178</t>
+          <t>417431</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>770715</t>
+          <t>772049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>799851</t>
+          <t>799966</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14297</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18030</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14131</t>
+          <t>13699</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29144</t>
+          <t>28335</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>135669</t>
+          <t>135355</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146151</t>
+          <t>146216</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>133012</t>
+          <t>133107</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>145390</t>
+          <t>145344</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>272849</t>
+          <t>272645</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>288988</t>
+          <t>289502</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8635</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26939</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>11813</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27193</t>
+          <t>27322</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>27552</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>48699</t>
+          <t>48472</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>25961</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45231</t>
+          <t>44887</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>37775</t>
+          <t>36207</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>60640</t>
+          <t>59442</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>68702</t>
+          <t>69328</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>96544</t>
+          <t>98039</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>586091</t>
+          <t>587242</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>609739</t>
+          <t>611351</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>607261</t>
+          <t>606017</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>633945</t>
+          <t>633183</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1202660</t>
+          <t>1201594</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1237306</t>
+          <t>1237832</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -7899,7 +7899,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>14440</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17545</t>
+          <t>18087</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47258</t>
+          <t>46649</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53875</t>
+          <t>53814</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50857</t>
+          <t>50800</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61441</t>
+          <t>61264</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>100884</t>
+          <t>100957</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>113472</t>
+          <t>113342</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>796</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>15788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24813</t>
+          <t>24750</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>19224</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36398</t>
+          <t>36463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46479</t>
+          <t>45016</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>67276</t>
+          <t>68035</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33785</t>
+          <t>33301</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55186</t>
+          <t>54468</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>85227</t>
+          <t>85434</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>115827</t>
+          <t>117034</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -8915,12 +8915,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>359494</t>
+          <t>358652</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>382948</t>
+          <t>383818</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>384221</t>
+          <t>385580</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>409373</t>
+          <t>410935</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>751782</t>
+          <t>751265</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>787734</t>
+          <t>786808</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9000,12 +9000,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,49%</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>9615</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16373</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18144</t>
+          <t>17761</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10334</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23547</t>
+          <t>23285</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20739</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37286</t>
+          <t>37325</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>130324</t>
+          <t>131795</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>143916</t>
+          <t>144391</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>140199</t>
+          <t>140911</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154607</t>
+          <t>154523</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>276520</t>
+          <t>276418</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>295886</t>
+          <t>295667</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24808</t>
+          <t>24576</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>15953</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32355</t>
+          <t>31679</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>30181</t>
+          <t>31093</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>52449</t>
+          <t>52231</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>60034</t>
+          <t>59004</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>84867</t>
+          <t>84980</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>56995</t>
+          <t>56309</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>82864</t>
+          <t>83322</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>121661</t>
+          <t>121350</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>158124</t>
+          <t>158034</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -10505,12 +10505,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>547148</t>
+          <t>547300</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>575405</t>
+          <t>576086</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10540,12 +10540,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>588596</t>
+          <t>587283</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>618102</t>
+          <t>616983</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1143914</t>
+          <t>1143461</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1184135</t>
+          <t>1185296</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -11192,12 +11192,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>494</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11207,12 +11207,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11242,12 +11242,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12280</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11277,12 +11277,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -11305,12 +11305,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>16169</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22313</t>
+          <t>22483</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11390,12 +11390,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -11418,12 +11418,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23712</t>
+          <t>22698</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11453,12 +11453,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21069</t>
+          <t>21179</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11468,12 +11468,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11488,12 +11488,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19721</t>
+          <t>19482</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40610</t>
+          <t>38046</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11503,12 +11503,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25388</t>
+          <t>24641</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41097</t>
+          <t>41178</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23524</t>
+          <t>23676</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37502</t>
+          <t>37922</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11601,12 +11601,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>52168</t>
+          <t>54054</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>74494</t>
+          <t>74572</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11616,12 +11616,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,89%</t>
         </is>
       </c>
     </row>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11987,12 +11987,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12027,7 +12027,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -12100,12 +12100,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13681</t>
+          <t>13602</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29052</t>
+          <t>28619</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12115,12 +12115,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12135,12 +12135,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29511</t>
+          <t>28507</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51663</t>
+          <t>50594</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12150,12 +12150,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12170,12 +12170,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46222</t>
+          <t>46528</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73078</t>
+          <t>72422</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12185,12 +12185,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -12213,12 +12213,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98149</t>
+          <t>99672</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>183853</t>
+          <t>190245</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12248,12 +12248,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>107097</t>
+          <t>105420</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>149362</t>
+          <t>147695</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12263,12 +12263,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12283,12 +12283,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>219727</t>
+          <t>219875</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>320059</t>
+          <t>321927</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12298,12 +12298,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>247581</t>
+          <t>243524</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>330029</t>
+          <t>328505</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>315038</t>
+          <t>314794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>358619</t>
+          <t>361639</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>583982</t>
+          <t>580662</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>675436</t>
+          <t>674315</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,46%</t>
         </is>
       </c>
     </row>
@@ -12822,7 +12822,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -12895,12 +12895,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10064</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12910,12 +12910,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>13893</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12945,12 +12945,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12965,12 +12965,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7457</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>21248</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12980,12 +12980,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -13008,12 +13008,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17461</t>
+          <t>17325</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32352</t>
+          <t>33084</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13023,12 +13023,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13043,12 +13043,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>19145</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35226</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41455</t>
+          <t>40923</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63699</t>
+          <t>62463</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -13121,12 +13121,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107798</t>
+          <t>106857</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>122954</t>
+          <t>124023</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13136,12 +13136,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136917</t>
+          <t>136640</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>155308</t>
+          <t>155581</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13191,12 +13191,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>248837</t>
+          <t>249418</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>273400</t>
+          <t>274075</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,73%</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13592,12 +13592,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13612,12 +13612,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13627,12 +13627,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13647,12 +13647,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13662,12 +13662,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -13690,12 +13690,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22162</t>
+          <t>22771</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39444</t>
+          <t>39738</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13725,12 +13725,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44196</t>
+          <t>45121</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71293</t>
+          <t>70735</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13760,12 +13760,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71567</t>
+          <t>71168</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>103655</t>
+          <t>102441</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -13803,12 +13803,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>137028</t>
+          <t>135628</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>250310</t>
+          <t>234528</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13818,12 +13818,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>147044</t>
+          <t>143449</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>192030</t>
+          <t>189261</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13873,12 +13873,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>296214</t>
+          <t>294804</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>413764</t>
+          <t>395629</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -13916,12 +13916,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>377221</t>
+          <t>387524</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>479638</t>
+          <t>480248</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13931,12 +13931,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>491430</t>
+          <t>490860</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>538922</t>
+          <t>540340</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13986,12 +13986,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>896048</t>
+          <t>911887</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1004113</t>
+          <t>1005297</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
